--- a/Luban/DataTables/Datas/Exdata.xlsx
+++ b/Luban/DataTables/Datas/Exdata.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="26640" windowHeight="8700"/>
+    <workbookView windowWidth="26880" windowHeight="9285"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1054,7 +1054,7 @@
     </row>
     <row r="5" spans="2:3">
       <c r="B5" s="1">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="C5" s="1">
         <v>0</v>
@@ -1062,7 +1062,7 @@
     </row>
     <row r="6" spans="2:3">
       <c r="B6" s="1">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="C6" s="1">
         <v>1000</v>

--- a/Luban/DataTables/Datas/Exdata.xlsx
+++ b/Luban/DataTables/Datas/Exdata.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="26880" windowHeight="9285"/>
+    <workbookView windowWidth="30705" windowHeight="9885"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="23">
   <si>
     <t>##var</t>
   </si>
@@ -35,7 +35,25 @@
     <t>id</t>
   </si>
   <si>
-    <t>value</t>
+    <t>##desc</t>
+  </si>
+  <si>
+    <t>initValue</t>
+  </si>
+  <si>
+    <t>maxValue</t>
+  </si>
+  <si>
+    <t>refreshRule</t>
+  </si>
+  <si>
+    <t>refreshTime</t>
+  </si>
+  <si>
+    <t>canClientChange</t>
+  </si>
+  <si>
+    <t>condition</t>
   </si>
   <si>
     <t>##type</t>
@@ -53,10 +71,31 @@
     <t>c,s</t>
   </si>
   <si>
+    <t>c</t>
+  </si>
+  <si>
     <t>##</t>
   </si>
   <si>
-    <t>数据</t>
+    <t>备注</t>
+  </si>
+  <si>
+    <t>初始值</t>
+  </si>
+  <si>
+    <t>最大值</t>
+  </si>
+  <si>
+    <t>刷新规则</t>
+  </si>
+  <si>
+    <t>刷新时间</t>
+  </si>
+  <si>
+    <t>client可修改</t>
+  </si>
+  <si>
+    <t>计入条件</t>
   </si>
 </sst>
 </file>
@@ -73,6 +112,13 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -188,13 +234,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="等线"/>
       <charset val="0"/>
@@ -231,6 +270,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -250,12 +295,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -542,55 +581,55 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -672,11 +711,20 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="22" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="22" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="22" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -998,74 +1046,870 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5" outlineLevelCol="2"/>
+  <dimension ref="A1:Y35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="20.375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="32.375" customWidth="1"/>
-    <col min="5" max="5" width="24.375" customWidth="1"/>
-    <col min="6" max="9" width="18" customWidth="1"/>
+    <col min="2" max="3" width="20.375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="15.625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="20.75" style="2" customWidth="1"/>
+    <col min="6" max="6" width="24.375" style="2" customWidth="1"/>
+    <col min="7" max="10" width="18" style="2" customWidth="1"/>
+    <col min="11" max="21" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:25">
+      <c r="A4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="4"/>
+      <c r="O4" s="4"/>
+      <c r="P4" s="4"/>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="4"/>
+      <c r="S4" s="4"/>
+      <c r="T4" s="4"/>
+      <c r="U4" s="4"/>
+      <c r="V4" s="4"/>
+      <c r="W4" s="4"/>
+      <c r="X4" s="4"/>
+      <c r="Y4" s="4"/>
+    </row>
+    <row r="5" s="1" customFormat="1" spans="1:25">
+      <c r="A5" s="3"/>
+      <c r="B5" s="4">
+        <v>0</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4">
+        <v>0</v>
+      </c>
+      <c r="E5" s="4">
+        <v>-1</v>
+      </c>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4"/>
+      <c r="M5" s="4"/>
+      <c r="N5" s="4"/>
+      <c r="O5" s="4"/>
+      <c r="P5" s="4"/>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="4"/>
+      <c r="S5" s="4"/>
+      <c r="T5" s="4"/>
+      <c r="U5" s="4"/>
+      <c r="V5" s="4"/>
+      <c r="W5" s="4"/>
+      <c r="X5" s="4"/>
+      <c r="Y5" s="4"/>
+    </row>
+    <row r="6" spans="2:9">
+      <c r="B6" s="2">
+        <v>1</v>
+      </c>
+      <c r="D6" s="2">
+        <v>0</v>
+      </c>
+      <c r="E6" s="2">
+        <v>-1</v>
+      </c>
+      <c r="F6" s="2">
+        <v>-1</v>
+      </c>
+      <c r="G6" s="2">
+        <v>-1</v>
+      </c>
+      <c r="H6" s="2">
+        <v>1</v>
+      </c>
+      <c r="I6" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9">
+      <c r="B7" s="2">
+        <v>2</v>
+      </c>
+      <c r="D7" s="2">
+        <v>1000</v>
+      </c>
+      <c r="E7" s="2">
+        <v>-1</v>
+      </c>
+      <c r="F7" s="2">
+        <v>-1</v>
+      </c>
+      <c r="G7" s="2">
+        <v>-1</v>
+      </c>
+      <c r="H7" s="2">
+        <v>1</v>
+      </c>
+      <c r="I7" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9">
+      <c r="B8" s="2">
         <v>3</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="D8" s="2">
+        <v>0</v>
+      </c>
+      <c r="E8" s="2">
+        <v>-1</v>
+      </c>
+      <c r="F8" s="2">
+        <v>-1</v>
+      </c>
+      <c r="G8" s="2">
+        <v>-1</v>
+      </c>
+      <c r="H8" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I8" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9">
+      <c r="B9" s="2">
         <v>4</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D9" s="2">
+        <v>0</v>
+      </c>
+      <c r="E9" s="2">
+        <v>-1</v>
+      </c>
+      <c r="F9" s="2">
+        <v>-1</v>
+      </c>
+      <c r="G9" s="2">
+        <v>-1</v>
+      </c>
+      <c r="H9" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I9" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9">
+      <c r="B10" s="2">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
+      <c r="D10" s="2">
+        <v>0</v>
+      </c>
+      <c r="E10" s="2">
+        <v>-1</v>
+      </c>
+      <c r="F10" s="2">
+        <v>-1</v>
+      </c>
+      <c r="G10" s="2">
+        <v>-1</v>
+      </c>
+      <c r="H10" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I10" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9">
+      <c r="B11" s="2">
         <v>6</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="D11" s="2">
+        <v>0</v>
+      </c>
+      <c r="E11" s="2">
+        <v>-1</v>
+      </c>
+      <c r="F11" s="2">
+        <v>-1</v>
+      </c>
+      <c r="G11" s="2">
+        <v>-1</v>
+      </c>
+      <c r="H11" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I11" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="12" spans="2:9">
+      <c r="B12" s="2">
         <v>7</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
+      <c r="D12" s="2">
+        <v>0</v>
+      </c>
+      <c r="E12" s="2">
+        <v>-1</v>
+      </c>
+      <c r="F12" s="2">
+        <v>-1</v>
+      </c>
+      <c r="G12" s="2">
+        <v>-1</v>
+      </c>
+      <c r="H12" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I12" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9">
+      <c r="B13" s="2">
         <v>8</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="1" t="s">
+      <c r="D13" s="2">
+        <v>0</v>
+      </c>
+      <c r="E13" s="2">
+        <v>-1</v>
+      </c>
+      <c r="F13" s="2">
+        <v>-1</v>
+      </c>
+      <c r="G13" s="2">
+        <v>-1</v>
+      </c>
+      <c r="H13" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I13" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9">
+      <c r="B14" s="2">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" spans="2:3">
-      <c r="B5" s="1">
-        <v>1001</v>
-      </c>
-      <c r="C5" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="2:3">
-      <c r="B6" s="1">
-        <v>1002</v>
-      </c>
-      <c r="C6" s="1">
-        <v>1000</v>
+      <c r="D14" s="2">
+        <v>0</v>
+      </c>
+      <c r="E14" s="2">
+        <v>-1</v>
+      </c>
+      <c r="F14" s="2">
+        <v>-1</v>
+      </c>
+      <c r="G14" s="2">
+        <v>-1</v>
+      </c>
+      <c r="H14" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I14" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9">
+      <c r="B15" s="2">
+        <v>10</v>
+      </c>
+      <c r="D15" s="2">
+        <v>0</v>
+      </c>
+      <c r="E15" s="2">
+        <v>-1</v>
+      </c>
+      <c r="F15" s="2">
+        <v>-1</v>
+      </c>
+      <c r="G15" s="2">
+        <v>-1</v>
+      </c>
+      <c r="H15" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I15" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9">
+      <c r="B16" s="2">
+        <v>11</v>
+      </c>
+      <c r="D16" s="2">
+        <v>0</v>
+      </c>
+      <c r="E16" s="2">
+        <v>-1</v>
+      </c>
+      <c r="F16" s="2">
+        <v>-1</v>
+      </c>
+      <c r="G16" s="2">
+        <v>-1</v>
+      </c>
+      <c r="H16" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I16" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9">
+      <c r="B17" s="2">
+        <v>12</v>
+      </c>
+      <c r="D17" s="2">
+        <v>0</v>
+      </c>
+      <c r="E17" s="2">
+        <v>-1</v>
+      </c>
+      <c r="F17" s="2">
+        <v>-1</v>
+      </c>
+      <c r="G17" s="2">
+        <v>-1</v>
+      </c>
+      <c r="H17" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I17" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9">
+      <c r="B18" s="2">
+        <v>13</v>
+      </c>
+      <c r="D18" s="2">
+        <v>0</v>
+      </c>
+      <c r="E18" s="2">
+        <v>-1</v>
+      </c>
+      <c r="F18" s="2">
+        <v>-1</v>
+      </c>
+      <c r="G18" s="2">
+        <v>-1</v>
+      </c>
+      <c r="H18" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I18" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9">
+      <c r="B19" s="2">
+        <v>14</v>
+      </c>
+      <c r="D19" s="2">
+        <v>0</v>
+      </c>
+      <c r="E19" s="2">
+        <v>-1</v>
+      </c>
+      <c r="F19" s="2">
+        <v>-1</v>
+      </c>
+      <c r="G19" s="2">
+        <v>-1</v>
+      </c>
+      <c r="H19" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I19" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9">
+      <c r="B20" s="2">
+        <v>15</v>
+      </c>
+      <c r="D20" s="2">
+        <v>0</v>
+      </c>
+      <c r="E20" s="2">
+        <v>-1</v>
+      </c>
+      <c r="F20" s="2">
+        <v>-1</v>
+      </c>
+      <c r="G20" s="2">
+        <v>-1</v>
+      </c>
+      <c r="H20" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I20" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9">
+      <c r="B21" s="2">
+        <v>16</v>
+      </c>
+      <c r="D21" s="2">
+        <v>0</v>
+      </c>
+      <c r="E21" s="2">
+        <v>-1</v>
+      </c>
+      <c r="F21" s="2">
+        <v>-1</v>
+      </c>
+      <c r="G21" s="2">
+        <v>-1</v>
+      </c>
+      <c r="H21" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I21" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9">
+      <c r="B22" s="2">
+        <v>17</v>
+      </c>
+      <c r="D22" s="2">
+        <v>0</v>
+      </c>
+      <c r="E22" s="2">
+        <v>-1</v>
+      </c>
+      <c r="F22" s="2">
+        <v>-1</v>
+      </c>
+      <c r="G22" s="2">
+        <v>-1</v>
+      </c>
+      <c r="H22" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I22" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9">
+      <c r="B23" s="2">
+        <v>18</v>
+      </c>
+      <c r="D23" s="2">
+        <v>0</v>
+      </c>
+      <c r="E23" s="2">
+        <v>-1</v>
+      </c>
+      <c r="F23" s="2">
+        <v>-1</v>
+      </c>
+      <c r="G23" s="2">
+        <v>-1</v>
+      </c>
+      <c r="H23" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I23" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9">
+      <c r="B24" s="2">
+        <v>19</v>
+      </c>
+      <c r="D24" s="2">
+        <v>0</v>
+      </c>
+      <c r="E24" s="2">
+        <v>-1</v>
+      </c>
+      <c r="F24" s="2">
+        <v>-1</v>
+      </c>
+      <c r="G24" s="2">
+        <v>-1</v>
+      </c>
+      <c r="H24" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I24" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9">
+      <c r="B25" s="2">
+        <v>20</v>
+      </c>
+      <c r="D25" s="2">
+        <v>0</v>
+      </c>
+      <c r="E25" s="2">
+        <v>-1</v>
+      </c>
+      <c r="F25" s="2">
+        <v>-1</v>
+      </c>
+      <c r="G25" s="2">
+        <v>-1</v>
+      </c>
+      <c r="H25" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I25" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="26" spans="2:9">
+      <c r="B26" s="2">
+        <v>21</v>
+      </c>
+      <c r="D26" s="2">
+        <v>0</v>
+      </c>
+      <c r="E26" s="2">
+        <v>-1</v>
+      </c>
+      <c r="F26" s="2">
+        <v>-1</v>
+      </c>
+      <c r="G26" s="2">
+        <v>-1</v>
+      </c>
+      <c r="H26" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I26" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="27" spans="2:9">
+      <c r="B27" s="2">
+        <v>22</v>
+      </c>
+      <c r="D27" s="2">
+        <v>0</v>
+      </c>
+      <c r="E27" s="2">
+        <v>-1</v>
+      </c>
+      <c r="F27" s="2">
+        <v>-1</v>
+      </c>
+      <c r="G27" s="2">
+        <v>-1</v>
+      </c>
+      <c r="H27" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I27" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="28" spans="2:9">
+      <c r="B28" s="2">
+        <v>23</v>
+      </c>
+      <c r="D28" s="2">
+        <v>0</v>
+      </c>
+      <c r="E28" s="2">
+        <v>-1</v>
+      </c>
+      <c r="F28" s="2">
+        <v>-1</v>
+      </c>
+      <c r="G28" s="2">
+        <v>-1</v>
+      </c>
+      <c r="H28" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I28" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="29" spans="2:9">
+      <c r="B29" s="2">
+        <v>24</v>
+      </c>
+      <c r="D29" s="2">
+        <v>0</v>
+      </c>
+      <c r="E29" s="2">
+        <v>-1</v>
+      </c>
+      <c r="F29" s="2">
+        <v>-1</v>
+      </c>
+      <c r="G29" s="2">
+        <v>-1</v>
+      </c>
+      <c r="H29" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I29" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="30" spans="2:9">
+      <c r="B30" s="2">
+        <v>25</v>
+      </c>
+      <c r="D30" s="2">
+        <v>0</v>
+      </c>
+      <c r="E30" s="2">
+        <v>-1</v>
+      </c>
+      <c r="F30" s="2">
+        <v>-1</v>
+      </c>
+      <c r="G30" s="2">
+        <v>-1</v>
+      </c>
+      <c r="H30" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I30" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="31" spans="2:9">
+      <c r="B31" s="2">
+        <v>26</v>
+      </c>
+      <c r="D31" s="2">
+        <v>0</v>
+      </c>
+      <c r="E31" s="2">
+        <v>-1</v>
+      </c>
+      <c r="F31" s="2">
+        <v>-1</v>
+      </c>
+      <c r="G31" s="2">
+        <v>-1</v>
+      </c>
+      <c r="H31" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I31" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="32" spans="2:9">
+      <c r="B32" s="2">
+        <v>27</v>
+      </c>
+      <c r="D32" s="2">
+        <v>0</v>
+      </c>
+      <c r="E32" s="2">
+        <v>-1</v>
+      </c>
+      <c r="F32" s="2">
+        <v>-1</v>
+      </c>
+      <c r="G32" s="2">
+        <v>-1</v>
+      </c>
+      <c r="H32" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I32" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="33" spans="2:9">
+      <c r="B33" s="2">
+        <v>28</v>
+      </c>
+      <c r="D33" s="2">
+        <v>0</v>
+      </c>
+      <c r="E33" s="2">
+        <v>-1</v>
+      </c>
+      <c r="F33" s="2">
+        <v>-1</v>
+      </c>
+      <c r="G33" s="2">
+        <v>-1</v>
+      </c>
+      <c r="H33" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I33" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="34" spans="2:9">
+      <c r="B34" s="2">
+        <v>29</v>
+      </c>
+      <c r="D34" s="2">
+        <v>0</v>
+      </c>
+      <c r="E34" s="2">
+        <v>-1</v>
+      </c>
+      <c r="F34" s="2">
+        <v>-1</v>
+      </c>
+      <c r="G34" s="2">
+        <v>-1</v>
+      </c>
+      <c r="H34" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I34" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="35" spans="2:9">
+      <c r="B35" s="2">
+        <v>30</v>
+      </c>
+      <c r="D35" s="2">
+        <v>0</v>
+      </c>
+      <c r="E35" s="2">
+        <v>-1</v>
+      </c>
+      <c r="F35" s="2">
+        <v>-1</v>
+      </c>
+      <c r="G35" s="2">
+        <v>-1</v>
+      </c>
+      <c r="H35" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I35" s="2">
+        <v>-1</v>
       </c>
     </row>
   </sheetData>
